--- a/diseases/d091/1995-1999.xlsx
+++ b/diseases/d091/1995-1999.xlsx
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">

--- a/diseases/d091/1995-1999.xlsx
+++ b/diseases/d091/1995-1999.xlsx
@@ -2422,7 +2422,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN22" t="b">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN24" t="b">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN32" t="b">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -14880,7 +14880,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -15280,7 +15280,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN76" t="b">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -16480,7 +16480,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -17280,7 +17280,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN86" t="b">
